--- a/系統分析/範本/yyyyMM(起)-yyyyMM(迄)-事件監控統計表_yyyyMMdd_hhmm.xlsx
+++ b/系統分析/範本/yyyyMM(起)-yyyyMM(迄)-事件監控統計表_yyyyMMdd_hhmm.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11590" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11590" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="災害事件一覽表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="99">
   <si>
     <t>NO</t>
   </si>
@@ -333,17 +333,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>土石流及大規模崩塌災害</t>
-  </si>
-  <si>
-    <t>毒性及關注化學物質災害</t>
-  </si>
-  <si>
     <t>其他</t>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>yyyyMM(起)-yyyyMM(迄)EMS災類與發生地點比較表</t>
@@ -368,6 +358,24 @@
   <si>
     <t>南區</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土石流</t>
+  </si>
+  <si>
+    <t>震災</t>
+  </si>
+  <si>
+    <t>生物病原</t>
+  </si>
+  <si>
+    <t>輻射</t>
+  </si>
+  <si>
+    <t>輸電線路災害</t>
+  </si>
+  <si>
+    <t>公用氣體與油料管線</t>
   </si>
 </sst>
 </file>
@@ -594,6 +602,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -620,15 +637,6 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,26 +931,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
@@ -1087,24 +1095,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
@@ -1157,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E5" s="8">
         <v>0</v>
@@ -1177,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="8">
         <v>0</v>
@@ -1197,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="E7" s="8">
         <v>0</v>
@@ -1217,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E8" s="8">
         <v>0</v>
@@ -1237,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" s="8">
         <v>0</v>
@@ -1257,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="8">
         <v>0</v>
@@ -1277,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" s="8">
         <v>0</v>
@@ -1298,7 +1306,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="E12" s="8">
         <v>2</v>
@@ -1319,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E13" s="8">
         <v>0</v>
@@ -1340,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E14" s="8">
         <v>0</v>
@@ -1361,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E15" s="8">
         <v>0</v>
@@ -1382,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="E16" s="8">
         <v>0</v>
@@ -1403,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E17" s="8">
         <v>0</v>
@@ -1424,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E18" s="8">
         <v>0</v>
@@ -1445,7 +1453,7 @@
         <v>0.4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E19" s="8">
         <v>4</v>
@@ -1466,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="E20" s="8">
         <v>0</v>
@@ -1487,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="E21" s="8">
         <v>0</v>
@@ -1528,15 +1536,9 @@
       <c r="C23" s="9">
         <v>0</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
       <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12" ht="19.5" x14ac:dyDescent="0.4">
@@ -1549,15 +1551,9 @@
       <c r="C24" s="9">
         <v>0.1</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0.1</v>
-      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
       <c r="L24" s="15"/>
     </row>
     <row r="25" spans="1:12" ht="19.5" x14ac:dyDescent="0.4">
@@ -1570,15 +1566,9 @@
       <c r="C25" s="9">
         <v>0</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9"/>
       <c r="L25" s="15"/>
     </row>
     <row r="26" spans="1:12" ht="19.5" x14ac:dyDescent="0.4">
@@ -1678,7 +1668,7 @@
       <c r="B32" s="11">
         <v>10</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="17">
         <v>1</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -1687,7 +1677,7 @@
       <c r="E32" s="11">
         <v>10</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="17">
         <v>1</v>
       </c>
     </row>
@@ -1714,18 +1704,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
@@ -1836,72 +1826,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
+      <c r="A1" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
     </row>
     <row r="3" spans="1:30" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
@@ -2363,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="11" t="s">
         <v>38</v>
       </c>
@@ -2467,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
@@ -2475,7 +2465,7 @@
     <col min="4" max="4" width="22" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14.90625" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
@@ -2483,70 +2473,63 @@
     <col min="15" max="15" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="26.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.7265625" style="7"/>
+    <col min="18" max="18" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="5.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+    <row r="1" spans="1:21" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A2" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-    </row>
-    <row r="3" spans="1:24" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+    </row>
+    <row r="3" spans="1:21" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
         <v>59</v>
       </c>
@@ -2554,73 +2537,64 @@
         <v>10</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="M3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="R3" s="11" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="T3" s="11" t="s">
         <v>35</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="X3" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>39</v>
       </c>
@@ -2684,17 +2658,8 @@
       <c r="U4" s="8">
         <v>0</v>
       </c>
-      <c r="V4" s="8">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -2758,17 +2723,8 @@
       <c r="U5" s="8">
         <v>0</v>
       </c>
-      <c r="V5" s="8">
-        <v>0</v>
-      </c>
-      <c r="W5" s="8">
-        <v>0</v>
-      </c>
-      <c r="X5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>41</v>
       </c>
@@ -2832,17 +2788,8 @@
       <c r="U6" s="8">
         <v>0</v>
       </c>
-      <c r="V6" s="8">
-        <v>0</v>
-      </c>
-      <c r="W6" s="8">
-        <v>0</v>
-      </c>
-      <c r="X6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -2906,17 +2853,8 @@
       <c r="U7" s="8">
         <v>0</v>
       </c>
-      <c r="V7" s="8">
-        <v>1</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" s="27" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:21" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="11" t="s">
         <v>38</v>
       </c>
@@ -2980,20 +2918,11 @@
       <c r="U8" s="11">
         <v>0</v>
       </c>
-      <c r="V8" s="11">
-        <v>1</v>
-      </c>
-      <c r="W8" s="11">
-        <v>0</v>
-      </c>
-      <c r="X8" s="11">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3200,27 +3129,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
       <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>44</v>
@@ -3254,7 +3183,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
@@ -3288,7 +3217,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
@@ -3322,7 +3251,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B9" s="8">
         <v>1</v>
@@ -3337,7 +3266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11" t="s">
         <v>38</v>
       </c>
@@ -3379,10 +3308,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="25"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">

--- a/系統分析/範本/yyyyMM(起)-yyyyMM(迄)-事件監控統計表_yyyyMMdd_hhmm.xlsx
+++ b/系統分析/範本/yyyyMM(起)-yyyyMM(迄)-事件監控統計表_yyyyMMdd_hhmm.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11590" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11590" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="災害事件一覽表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="97">
   <si>
     <t>NO</t>
   </si>
@@ -150,10 +150,6 @@
   </si>
   <si>
     <t>懸浮微粒物質災害</t>
-  </si>
-  <si>
-    <t>合計</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>桃園市</t>
@@ -222,9 +218,6 @@
   <si>
     <t>yyyyMM(起)-yyyyMM(迄)災類統計</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合  計</t>
   </si>
   <si>
     <t>yyyyMM(起)-yyyyMM(迄)災害地區統計表</t>
@@ -932,7 +925,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -944,7 +937,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
       <c r="B2" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -957,22 +950,22 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -980,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3">
         <v>45989.488888888889</v>
@@ -992,7 +985,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1003,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3">
         <v>45976.488888888889</v>
@@ -1015,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G5" s="2">
         <v>3</v>
@@ -1026,7 +1019,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3">
         <v>45969.488888888889</v>
@@ -1038,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1049,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3">
         <v>45962.488888888889</v>
@@ -1096,7 +1089,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1106,7 +1099,7 @@
     </row>
     <row r="2" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1116,22 +1109,22 @@
     </row>
     <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -1165,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" s="8">
         <v>0</v>
@@ -1205,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" s="8">
         <v>0</v>
@@ -1225,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E8" s="8">
         <v>0</v>
@@ -1306,7 +1299,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12" s="8">
         <v>2</v>
@@ -1390,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E16" s="8">
         <v>0</v>
@@ -1474,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E20" s="8">
         <v>0</v>
@@ -1495,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E21" s="8">
         <v>0</v>
@@ -1663,7 +1656,7 @@
     </row>
     <row r="32" spans="1:12" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32" s="11">
         <v>10</v>
@@ -1672,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E32" s="11">
         <v>10</v>
@@ -1705,21 +1698,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>8</v>
@@ -1730,7 +1723,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
@@ -1741,7 +1734,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2">
         <v>3</v>
@@ -1752,7 +1745,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1763,7 +1756,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -1773,13 +1766,13 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="A8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11">
+        <v>10</v>
+      </c>
+      <c r="C8" s="17">
         <v>1</v>
       </c>
     </row>
@@ -1827,7 +1820,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1861,7 +1854,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A2" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -1895,7 +1888,7 @@
     </row>
     <row r="3" spans="1:30" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>10</v>
@@ -1982,12 +1975,12 @@
         <v>37</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="8">
         <v>0</v>
@@ -2079,7 +2072,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="8">
         <v>3</v>
@@ -2171,7 +2164,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
@@ -2263,7 +2256,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -2354,8 +2347,8 @@
       </c>
     </row>
     <row r="8" spans="1:30" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
-        <v>38</v>
+      <c r="A8" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="B8" s="11">
         <v>3</v>
@@ -2481,7 +2474,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2506,7 +2499,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -2531,22 +2524,22 @@
     </row>
     <row r="3" spans="1:21" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>23</v>
@@ -2558,7 +2551,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>15</v>
@@ -2570,7 +2563,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>17</v>
@@ -2582,21 +2575,21 @@
         <v>33</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T3" s="11" t="s">
         <v>35</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="8">
         <v>0</v>
@@ -2661,7 +2654,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="8">
         <v>3</v>
@@ -2726,7 +2719,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
@@ -2791,72 +2784,72 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
+      </c>
+      <c r="S7" s="8">
+        <v>0</v>
+      </c>
+      <c r="T7" s="8">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="B8" s="11">
         <v>3</v>
@@ -3130,7 +3123,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -3140,7 +3133,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -3149,24 +3142,24 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -3183,7 +3176,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
@@ -3200,7 +3193,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="8">
         <v>1</v>
@@ -3217,7 +3210,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
@@ -3234,7 +3227,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B8" s="8">
         <v>1</v>
@@ -3251,7 +3244,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8">
         <v>1</v>
@@ -3267,8 +3260,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="11" t="s">
-        <v>38</v>
+      <c r="A10" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="B10" s="11">
         <v>5</v>
@@ -3309,56 +3302,56 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
